--- a/projektmanagement/GanntDiagramm.xlsx
+++ b/projektmanagement/GanntDiagramm.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE441170-CEDA-8248-A5C5-1AEABDB55CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5577C0A8-8916-824C-97DD-90764678E3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1429,10 +1429,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9" s="8">
         <v>0</v>
@@ -1469,10 +1469,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11" s="8">
         <v>0</v>
@@ -1509,10 +1509,10 @@
         <v>7</v>
       </c>
       <c r="E13" s="7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F13" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13" s="8">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F17" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17" s="8">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F21" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="8">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F22" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8">
         <v>0</v>
